--- a/Data_Product/App_Data/BBGN.xlsx
+++ b/Data_Product/App_Data/BBGN.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Software\Data_Product\Data_Product\App_Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Software\03. ThongKePKH\DATAPRODUCT_DEV\Data_Product\App_Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{283623DD-BD3F-46C2-AAF9-E215928DA579}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF408572-E79D-4139-995B-AAEACD357C73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12225" xr2:uid="{C55D740C-D1E6-4AF1-8652-5A16423F5332}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{C55D740C-D1E6-4AF1-8652-5A16423F5332}"/>
   </bookViews>
   <sheets>
     <sheet name="BBGN" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="20">
   <si>
     <t>TỔNG HỢP DỮ LIỆU BIÊN BẢN GIAO NHẬN NGUYÊN/NHIÊN/VẬT LIỆU</t>
   </si>
@@ -85,6 +85,9 @@
   </si>
   <si>
     <t>Bộ phận</t>
+  </si>
+  <si>
+    <t>Tên NVL2</t>
   </si>
 </sst>
 </file>
@@ -333,7 +336,6 @@
     <xf numFmtId="165" fontId="7" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -389,6 +391,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -459,9 +464,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -499,7 +504,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -605,7 +610,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -747,7 +752,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -755,121 +760,92 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{756BAF69-AE4A-460A-B70D-7F98F75C7929}">
-  <dimension ref="A1:T31"/>
+  <dimension ref="A1:U31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.5703125" style="8" customWidth="1"/>
-    <col min="2" max="2" width="23.5703125" style="8" customWidth="1"/>
-    <col min="3" max="3" width="10.5703125" style="8" customWidth="1"/>
-    <col min="4" max="4" width="12.42578125" style="8" customWidth="1"/>
-    <col min="5" max="5" width="27.7109375" style="8" customWidth="1"/>
-    <col min="6" max="6" width="29.28515625" style="8" customWidth="1"/>
-    <col min="7" max="8" width="16.140625" style="8" customWidth="1"/>
-    <col min="9" max="10" width="16.85546875" style="8" customWidth="1"/>
-    <col min="11" max="11" width="24" style="8" customWidth="1"/>
-    <col min="12" max="12" width="28.42578125" style="8" customWidth="1"/>
-    <col min="13" max="15" width="16.85546875" style="8" customWidth="1"/>
-    <col min="16" max="16" width="32.5703125" style="8" customWidth="1"/>
-    <col min="17" max="17" width="32" style="8" customWidth="1"/>
-    <col min="18" max="18" width="16.85546875" style="8" customWidth="1"/>
-    <col min="19" max="19" width="26.85546875" style="8" customWidth="1"/>
-    <col min="20" max="20" width="16.85546875" style="8" customWidth="1"/>
-    <col min="21" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="9.5703125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="23.5703125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="10.5703125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="12.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="27.7109375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="29.28515625" style="1" customWidth="1"/>
+    <col min="7" max="8" width="16.140625" style="1" customWidth="1"/>
+    <col min="9" max="10" width="16.85546875" style="1" customWidth="1"/>
+    <col min="11" max="11" width="24" style="1" customWidth="1"/>
+    <col min="12" max="12" width="28.42578125" style="1" customWidth="1"/>
+    <col min="13" max="15" width="16.85546875" style="1" customWidth="1"/>
+    <col min="16" max="16" width="32.5703125" style="1" customWidth="1"/>
+    <col min="17" max="17" width="32" style="1" customWidth="1"/>
+    <col min="18" max="18" width="16.85546875" style="1" customWidth="1"/>
+    <col min="19" max="19" width="26.85546875" style="1" customWidth="1"/>
+    <col min="20" max="20" width="16.85546875" style="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" customWidth="1"/>
+    <col min="22" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="9"/>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
-      <c r="O1" s="1"/>
-      <c r="P1" s="1"/>
-      <c r="Q1" s="1"/>
-      <c r="R1" s="1"/>
-      <c r="S1" s="1"/>
-      <c r="T1" s="1"/>
+    <row r="1" spans="1:21" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="8"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
     </row>
-    <row r="2" spans="1:20" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="9"/>
-      <c r="B2" s="9"/>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
-      <c r="N2" s="1"/>
-      <c r="O2" s="1"/>
-      <c r="P2" s="1"/>
-      <c r="Q2" s="1"/>
-      <c r="R2" s="1"/>
-      <c r="S2" s="1"/>
-      <c r="T2" s="1"/>
+    <row r="2" spans="1:21" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="8"/>
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
     </row>
-    <row r="3" spans="1:20" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="10" t="s">
+    <row r="3" spans="1:21" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="10"/>
-      <c r="C3" s="10"/>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="10"/>
-      <c r="G3" s="10"/>
-      <c r="H3" s="10"/>
-      <c r="I3" s="10"/>
-      <c r="J3" s="10"/>
-      <c r="K3" s="10"/>
-      <c r="L3" s="10"/>
-      <c r="M3" s="10"/>
-      <c r="N3" s="10"/>
-      <c r="O3" s="10"/>
-      <c r="P3" s="10"/>
-      <c r="Q3" s="10"/>
-      <c r="R3" s="10"/>
-      <c r="S3" s="10"/>
-      <c r="T3" s="10"/>
+      <c r="B3" s="9"/>
+      <c r="C3" s="9"/>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="9"/>
+      <c r="I3" s="9"/>
+      <c r="J3" s="9"/>
+      <c r="K3" s="9"/>
+      <c r="L3" s="9"/>
+      <c r="M3" s="9"/>
+      <c r="N3" s="9"/>
+      <c r="O3" s="9"/>
+      <c r="P3" s="9"/>
+      <c r="Q3" s="9"/>
+      <c r="R3" s="9"/>
+      <c r="S3" s="9"/>
+      <c r="T3" s="9"/>
     </row>
-    <row r="4" spans="1:20" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="11" t="s">
+    <row r="4" spans="1:21" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="11"/>
-      <c r="C4" s="11"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="11"/>
-      <c r="F4" s="11"/>
-      <c r="G4" s="11"/>
-      <c r="H4" s="11"/>
-      <c r="I4" s="11"/>
-      <c r="J4" s="11"/>
-      <c r="K4" s="11"/>
-      <c r="L4" s="11"/>
-      <c r="M4" s="11"/>
-      <c r="N4" s="11"/>
-      <c r="O4" s="11"/>
-      <c r="P4" s="11"/>
-      <c r="Q4" s="11"/>
-      <c r="R4" s="11"/>
-      <c r="S4" s="11"/>
-      <c r="T4" s="11"/>
+      <c r="B4" s="10"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="10"/>
+      <c r="I4" s="10"/>
+      <c r="J4" s="10"/>
+      <c r="K4" s="10"/>
+      <c r="L4" s="10"/>
+      <c r="M4" s="10"/>
+      <c r="N4" s="10"/>
+      <c r="O4" s="10"/>
+      <c r="P4" s="10"/>
+      <c r="Q4" s="10"/>
+      <c r="R4" s="10"/>
+      <c r="S4" s="10"/>
+      <c r="T4" s="10"/>
     </row>
-    <row r="5" spans="1:20" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:21" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -888,85 +864,87 @@
       <c r="P5" s="3"/>
       <c r="Q5" s="3"/>
       <c r="R5" s="3"/>
-      <c r="S5" s="1"/>
-      <c r="T5" s="1"/>
     </row>
-    <row r="6" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="12" t="s">
+    <row r="6" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="23" t="s">
+      <c r="C6" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="23" t="s">
+      <c r="D6" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="E6" s="12" t="s">
+      <c r="E6" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="F6" s="12" t="s">
+      <c r="F6" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="G6" s="12" t="s">
+      <c r="G6" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="H6" s="14" t="s">
+      <c r="H6" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="I6" s="15"/>
-      <c r="J6" s="15"/>
-      <c r="K6" s="15"/>
-      <c r="L6" s="16"/>
-      <c r="M6" s="14" t="s">
+      <c r="I6" s="14"/>
+      <c r="J6" s="14"/>
+      <c r="K6" s="14"/>
+      <c r="L6" s="15"/>
+      <c r="M6" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="N6" s="15"/>
-      <c r="O6" s="15"/>
-      <c r="P6" s="15"/>
-      <c r="Q6" s="16"/>
-      <c r="R6" s="25" t="s">
+      <c r="N6" s="14"/>
+      <c r="O6" s="14"/>
+      <c r="P6" s="14"/>
+      <c r="Q6" s="15"/>
+      <c r="R6" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="S6" s="27" t="s">
+      <c r="S6" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="T6" s="20" t="s">
+      <c r="T6" s="19" t="s">
         <v>13</v>
       </c>
+      <c r="U6" s="27" t="s">
+        <v>19</v>
+      </c>
     </row>
-    <row r="7" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="12"/>
-      <c r="B7" s="12"/>
-      <c r="C7" s="23"/>
-      <c r="D7" s="23"/>
-      <c r="E7" s="12"/>
-      <c r="F7" s="12"/>
-      <c r="G7" s="12"/>
-      <c r="H7" s="17"/>
-      <c r="I7" s="18"/>
-      <c r="J7" s="18"/>
-      <c r="K7" s="18"/>
-      <c r="L7" s="19"/>
-      <c r="M7" s="14"/>
-      <c r="N7" s="15"/>
-      <c r="O7" s="15"/>
-      <c r="P7" s="15"/>
-      <c r="Q7" s="16"/>
-      <c r="R7" s="25"/>
-      <c r="S7" s="27"/>
-      <c r="T7" s="21"/>
+    <row r="7" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="11"/>
+      <c r="B7" s="11"/>
+      <c r="C7" s="22"/>
+      <c r="D7" s="22"/>
+      <c r="E7" s="11"/>
+      <c r="F7" s="11"/>
+      <c r="G7" s="11"/>
+      <c r="H7" s="16"/>
+      <c r="I7" s="17"/>
+      <c r="J7" s="17"/>
+      <c r="K7" s="17"/>
+      <c r="L7" s="18"/>
+      <c r="M7" s="13"/>
+      <c r="N7" s="14"/>
+      <c r="O7" s="14"/>
+      <c r="P7" s="14"/>
+      <c r="Q7" s="15"/>
+      <c r="R7" s="24"/>
+      <c r="S7" s="26"/>
+      <c r="T7" s="20"/>
+      <c r="U7" s="27"/>
     </row>
-    <row r="8" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="13"/>
-      <c r="B8" s="13"/>
-      <c r="C8" s="24"/>
-      <c r="D8" s="24"/>
-      <c r="E8" s="13"/>
-      <c r="F8" s="13"/>
-      <c r="G8" s="13"/>
+    <row r="8" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="12"/>
+      <c r="B8" s="12"/>
+      <c r="C8" s="23"/>
+      <c r="D8" s="23"/>
+      <c r="E8" s="12"/>
+      <c r="F8" s="12"/>
+      <c r="G8" s="12"/>
       <c r="H8" s="4" t="s">
         <v>14</v>
       </c>
@@ -997,18 +975,19 @@
       <c r="Q8" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="R8" s="26"/>
-      <c r="S8" s="27"/>
-      <c r="T8" s="22"/>
+      <c r="R8" s="25"/>
+      <c r="S8" s="26"/>
+      <c r="T8" s="21"/>
+      <c r="U8" s="27"/>
     </row>
-    <row r="9" spans="1:20" ht="44.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10" spans="1:20" ht="44.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11" spans="1:20" ht="44.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12" spans="1:20" ht="44.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13" spans="1:20" ht="44.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14" spans="1:20" ht="44.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15" spans="1:20" ht="44.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16" spans="1:20" ht="44.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="1:21" ht="44.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10" spans="1:21" ht="44.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="1:21" ht="44.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12" spans="1:21" ht="44.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="1:21" ht="44.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="1:21" ht="44.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15" spans="1:21" ht="44.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16" spans="1:21" ht="44.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="17" ht="44.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="18" ht="44.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="19" ht="44.25" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -1025,7 +1004,8 @@
     <row r="30" ht="44.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="31" ht="44.25" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="16">
+    <mergeCell ref="U6:U8"/>
     <mergeCell ref="A1:E2"/>
     <mergeCell ref="A3:T3"/>
     <mergeCell ref="A4:T4"/>
